--- a/cobot-market-analysis.xlsx
+++ b/cobot-market-analysis.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Win\Documents\Studium\BA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F32CB8-03C8-44ED-B442-807FF26C4F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F79DAF-D399-4D1E-AA07-E515504DBEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores" sheetId="5" r:id="rId1"/>
     <sheet name="Ranking" sheetId="6" r:id="rId2"/>
-    <sheet name="GraphsAndCharts" sheetId="7" r:id="rId3"/>
+    <sheet name="GraphsAndTables" sheetId="7" r:id="rId3"/>
     <sheet name="RawCobots" sheetId="1" r:id="rId4"/>
     <sheet name="ScoringCriteria" sheetId="8" r:id="rId5"/>
     <sheet name="RawScoringCriteria" sheetId="2" state="hidden" r:id="rId6"/>
@@ -23,7 +23,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Ranking!$B$2:$B$162</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Ranking!$B$2:$B$162</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1915,6 +1914,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1935,9 +1937,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4500,7 +4499,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>GraphsAndCharts!$B$2</c:f>
+              <c:f>GraphsAndTables!$B$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4579,7 +4578,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>GraphsAndCharts!$A$3:$A$9</c:f>
+              <c:f>GraphsAndTables!$A$3:$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -4608,7 +4607,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GraphsAndCharts!$B$3:$B$9</c:f>
+              <c:f>GraphsAndTables!$B$3:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4647,7 +4646,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>GraphsAndCharts!$C$2</c:f>
+              <c:f>GraphsAndTables!$C$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4726,7 +4725,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>GraphsAndCharts!$A$3:$A$9</c:f>
+              <c:f>GraphsAndTables!$A$3:$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -4755,7 +4754,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GraphsAndCharts!$C$3:$C$9</c:f>
+              <c:f>GraphsAndTables!$C$3:$C$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5090,7 +5089,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>GraphsAndCharts!$E$61</c:f>
+              <c:f>GraphsAndTables!$E$61</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5169,7 +5168,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>GraphsAndCharts!$D$62:$D$71</c:f>
+              <c:f>GraphsAndTables!$D$62:$D$71</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -5207,7 +5206,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GraphsAndCharts!$E$62:$E$71</c:f>
+              <c:f>GraphsAndTables!$E$62:$E$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -5477,7 +5476,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -37547,7 +37546,7 @@
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.5703125" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -37960,14 +37959,14 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="69" t="s">
+      <c r="A26" s="62" t="s">
         <v>440</v>
       </c>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
       <c r="H26" s="53" t="s">
         <v>457</v>
       </c>
@@ -38296,7 +38295,7 @@
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
     <col min="2" max="2" width="29.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="5"/>
     <col min="6" max="6" width="12.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -51644,41 +51643,41 @@
       <c r="C179" t="s">
         <v>379</v>
       </c>
-      <c r="D179" s="62" cm="1">
+      <c r="D179" s="63" cm="1">
         <f t="array" ref="D179">SUM((D2:D177=E2:E177)*1)</f>
         <v>50</v>
       </c>
-      <c r="E179" s="63"/>
+      <c r="E179" s="64"/>
     </row>
     <row r="180" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C180" t="s">
         <v>381</v>
       </c>
-      <c r="D180" s="62">
+      <c r="D180" s="63">
         <f>D178+E178-D179</f>
         <v>176</v>
       </c>
-      <c r="E180" s="63"/>
+      <c r="E180" s="64"/>
     </row>
     <row r="181" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C181" t="s">
         <v>382</v>
       </c>
-      <c r="D181" s="62">
+      <c r="D181" s="63">
         <f>COUNTIF(AC2:AC177,"Y")</f>
         <v>15</v>
       </c>
-      <c r="E181" s="63"/>
+      <c r="E181" s="64"/>
     </row>
     <row r="182" spans="1:28" x14ac:dyDescent="0.25">
       <c r="C182" t="s">
         <v>380</v>
       </c>
-      <c r="D182" s="62">
+      <c r="D182" s="63">
         <f>D180-D181</f>
         <v>161</v>
       </c>
-      <c r="E182" s="63"/>
+      <c r="E182" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -51795,30 +51794,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="66" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="68" t="s">
         <v>183</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="66" t="s">
         <v>404</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="66" t="s">
         <v>411</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="63" t="s">
         <v>410</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
       <c r="E2" s="6" t="s">
         <v>418</v>
       </c>
@@ -53074,18 +53073,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -53278,14 +53277,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7861549-30F5-4008-9CD8-3C355FD5677F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C75C10-AC9C-47C5-8597-8A1CAA9D627A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="56bf95f3-df1f-45c4-9ad4-fd67310af48c"/>
@@ -53298,6 +53289,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7861549-30F5-4008-9CD8-3C355FD5677F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
